--- a/attached_assets/reports/critical-feedback-priorities.xlsx
+++ b/attached_assets/reports/critical-feedback-priorities.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Priorities (Prioridades)" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Clusters (Repetición)" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Roadmap (Hoja de Ruta)" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Out-of-scope (Fuera de alcance)" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="OOS deferred (Fuera de alcance)" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Methodology (Metodología)" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
